--- a/Table/PropTable.xlsx
+++ b/Table/PropTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Public\MiniGame-PushPush\TableData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\MiniGame-PushPush\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD70635-D253-4C7F-A281-A0A70EA333AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0302D401-2859-4937-A82D-3FC8FA0CCE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3528" yWindow="1464" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{DE230F5E-A5A3-422C-B9F2-AA52C2C5EF78}"/>
+    <workbookView xWindow="1185" yWindow="3660" windowWidth="26460" windowHeight="15435" xr2:uid="{DE230F5E-A5A3-422C-B9F2-AA52C2C5EF78}"/>
   </bookViews>
   <sheets>
     <sheet name="PropInfo" sheetId="1" r:id="rId1"/>
@@ -328,22 +328,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PointItem_Crate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PointItem_Cone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PointItem_Car</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PointItem_Plane</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ItemType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -369,6 +353,22 @@
   </si>
   <si>
     <t>Plane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResultItem_Crate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResultItem_Cone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResultItem_Car</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResultItem_Plane</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -455,9 +455,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -495,7 +495,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -601,7 +601,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -743,7 +743,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -752,15 +752,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247803B3-E396-4CB1-BF90-DE5E2BACEB81}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -789,7 +789,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -816,7 +816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -839,13 +839,13 @@
         <v>2500</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -868,13 +868,13 @@
         <v>2000</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -897,13 +897,13 @@
         <v>2500</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -926,13 +926,13 @@
         <v>3000</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -955,13 +955,13 @@
         <v>2500</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -984,13 +984,13 @@
         <v>2500</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1013,13 +1013,13 @@
         <v>3000</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1042,13 +1042,13 @@
         <v>2000</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1071,13 +1071,13 @@
         <v>5000</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1100,13 +1100,13 @@
         <v>2000</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1129,13 +1129,13 @@
         <v>2000</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1158,13 +1158,13 @@
         <v>1000</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1187,13 +1187,13 @@
         <v>5000</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1216,13 +1216,13 @@
         <v>3500</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1245,13 +1245,13 @@
         <v>1000</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>500</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
         <v>74</v>
@@ -1289,9 +1289,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F629A7F8-2502-4BD4-86F8-A1870B94E9C7}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1305,10 +1305,10 @@
         <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1337,10 +1337,10 @@
         <v>3500</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1354,10 +1354,10 @@
         <v>6500</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1371,10 +1371,10 @@
         <v>5000</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>2000</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1400,12 +1400,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2462192C-A044-4008-B7FF-602FEB57C699}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1510,13 +1510,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6688CC12-8DFC-4F47-883D-1195C6A04322}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>59</v>
@@ -1533,7 +1533,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>100</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -1565,7 +1565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>101</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>102</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>62</v>
@@ -1599,7 +1599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>103</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>104</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
